--- a/client/public/Team_Members_Template.xlsx
+++ b/client/public/Team_Members_Template.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <workbookPr codeName="ThisWorkbook"/>
   <sheets>
-    <sheet name="Team Members" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
 </workbook>
 </file>
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P4"/>
+  <dimension ref="A1:P5"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -416,41 +416,41 @@
         <v>Role</v>
       </c>
       <c r="F1" t="str">
+        <v>Branch</v>
+      </c>
+      <c r="G1" t="str">
+        <v>Image_URL</v>
+      </c>
+      <c r="H1" t="str">
+        <v>LinkedIn</v>
+      </c>
+      <c r="I1" t="str">
+        <v>Instagram</v>
+      </c>
+      <c r="J1" t="str">
+        <v>Contact</v>
+      </c>
+      <c r="K1" t="str">
+        <v>Why_Join</v>
+      </c>
+      <c r="L1" t="str">
+        <v>POR</v>
+      </c>
+      <c r="M1" t="str">
+        <v>Hobbies</v>
+      </c>
+      <c r="N1" t="str">
+        <v>Priority_ID</v>
+      </c>
+      <c r="O1" t="str">
+        <v>Sub_Priority</v>
+      </c>
+      <c r="P1" t="str">
         <v>Group</v>
-      </c>
-      <c r="G1" t="str">
-        <v>Priority_ID</v>
-      </c>
-      <c r="H1" t="str">
-        <v>Sub_Priority</v>
-      </c>
-      <c r="I1" t="str">
-        <v>Branch</v>
-      </c>
-      <c r="J1" t="str">
-        <v>Image_URL</v>
-      </c>
-      <c r="K1" t="str">
-        <v>LinkedIn</v>
-      </c>
-      <c r="L1" t="str">
-        <v>Instagram</v>
-      </c>
-      <c r="M1" t="str">
-        <v>Contact</v>
-      </c>
-      <c r="N1" t="str">
-        <v>Why_Join</v>
-      </c>
-      <c r="O1" t="str">
-        <v>POR</v>
-      </c>
-      <c r="P1" t="str">
-        <v>Hobbies</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="str">
+      <c r="A2">
         <v>240001001</v>
       </c>
       <c r="B2" t="str">
@@ -466,41 +466,32 @@
         <v>Head</v>
       </c>
       <c r="F2" t="str">
-        <v>Head</v>
-      </c>
-      <c r="G2">
-        <v>0</v>
-      </c>
-      <c r="H2">
-        <v>0</v>
+        <v>Mechanical Engineering</v>
+      </c>
+      <c r="G2" t="str">
+        <v>https://drive.google.com/file/d/XXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXX/view?usp=sharing</v>
+      </c>
+      <c r="H2" t="str">
+        <v>https://www.linkedin.com/in/anshkyal/</v>
       </c>
       <c r="I2" t="str">
-        <v>Mechanical Engineering</v>
-      </c>
-      <c r="J2" t="str">
-        <v>../Team/Ansh Kyal_Head.png</v>
+        <v>https://www.instagram.com/ansh_kyal29/</v>
+      </c>
+      <c r="J2">
+        <v>8391973739</v>
       </c>
       <c r="K2" t="str">
-        <v>https://www.linkedin.com/in/anshkyal/</v>
+        <v>To connect alumni and foster strong community relationships.</v>
       </c>
       <c r="L2" t="str">
-        <v>https://www.instagram.com/ansh_kyal29/</v>
+        <v>Alumni Cell Overall Head (2025-26)</v>
       </c>
       <c r="M2" t="str">
-        <v>8391973739</v>
-      </c>
-      <c r="N2" t="str">
-        <v>To connect alumni and foster strong community relationships.</v>
-      </c>
-      <c r="O2" t="str">
-        <v>Alumni Cell Overall Head (2025-26)</v>
-      </c>
-      <c r="P2" t="str">
         <v>Reading, Music</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="str">
+      <c r="A3">
         <v>240001002</v>
       </c>
       <c r="B3" t="str">
@@ -516,41 +507,32 @@
         <v>Head</v>
       </c>
       <c r="F3" t="str">
-        <v>Head</v>
-      </c>
-      <c r="G3">
-        <v>1</v>
-      </c>
-      <c r="H3">
-        <v>0</v>
+        <v>Computer Science and Engineering</v>
+      </c>
+      <c r="G3" t="str">
+        <v>https://drive.google.com/file/d/YYYYYYYYYYYYYYYYYYYYYYYYYYYYYYYY/view?usp=sharing</v>
+      </c>
+      <c r="H3" t="str">
+        <v>https://www.linkedin.com/in/yashasvi-shukla-49882030a/</v>
       </c>
       <c r="I3" t="str">
-        <v>Computer Science and Engineering</v>
-      </c>
-      <c r="J3" t="str">
-        <v>../Team/YashasviShukla.png</v>
+        <v>https://www.instagram.com/_.yashasvi.__/</v>
+      </c>
+      <c r="J3">
+        <v>6393626042</v>
       </c>
       <c r="K3" t="str">
-        <v>https://www.linkedin.com/in/yashasvi-shukla-49882030a/</v>
+        <v>Passionate about building scalable web solutions for ACell.</v>
       </c>
       <c r="L3" t="str">
-        <v>https://www.instagram.com/_.yashasvi.__/</v>
+        <v>Web Dev Head (2025-26)</v>
       </c>
       <c r="M3" t="str">
-        <v>6393626042</v>
-      </c>
-      <c r="N3" t="str">
-        <v>Passionate about building scalable web solutions for ACell.</v>
-      </c>
-      <c r="O3" t="str">
-        <v>Web Dev Head (2025-26)</v>
-      </c>
-      <c r="P3" t="str">
         <v>Web Development, Open Source</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="str">
+      <c r="A4">
         <v>240001003</v>
       </c>
       <c r="B4" t="str">
@@ -566,42 +548,71 @@
         <v>Team Lead</v>
       </c>
       <c r="F4" t="str">
+        <v>Electrical Engineering</v>
+      </c>
+      <c r="G4" t="str">
+        <v>https://drive.google.com/open?id=ZZZZZZZZZZZZZZZZZZZZZZZZZZZZZZZZ</v>
+      </c>
+      <c r="H4" t="str">
+        <v>https://www.linkedin.com/in/aviral-sharma-b57127299/</v>
+      </c>
+      <c r="J4">
+        <v>9876543210</v>
+      </c>
+      <c r="K4" t="str">
+        <v>To contribute to technical projects and collaborate with peers.</v>
+      </c>
+      <c r="L4" t="str">
+        <v>Web Dev Core Member (2025-26)</v>
+      </c>
+      <c r="M4" t="str">
+        <v>Competitive Programming, Gaming</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5">
+        <v>240001004</v>
+      </c>
+      <c r="B5" t="str">
+        <v>Priya Patel</v>
+      </c>
+      <c r="C5">
+        <v>2026</v>
+      </c>
+      <c r="D5" t="str">
+        <v>Design</v>
+      </c>
+      <c r="E5" t="str">
         <v>Member</v>
       </c>
-      <c r="G4">
-        <v>1</v>
-      </c>
-      <c r="H4">
-        <v>2</v>
-      </c>
-      <c r="I4" t="str">
-        <v>Electrical Engineering</v>
-      </c>
-      <c r="J4" t="str">
-        <v>../Team/AviralSharma.jpg</v>
-      </c>
-      <c r="K4" t="str">
-        <v>https://www.linkedin.com/in/aviral-sharma-b57127299/</v>
-      </c>
-      <c r="L4" t="str">
-        <v/>
-      </c>
-      <c r="M4" t="str">
-        <v>9876543210</v>
-      </c>
-      <c r="N4" t="str">
-        <v>To contribute to technical projects and collaborate with peers.</v>
-      </c>
-      <c r="O4" t="str">
-        <v>Web Dev Core Member (2025-26)</v>
-      </c>
-      <c r="P4" t="str">
-        <v>Competitive Programming, Gaming</v>
+      <c r="F5" t="str">
+        <v>Civil Engineering</v>
+      </c>
+      <c r="G5" t="str">
+        <v>https://drive.google.com/file/d/AAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAA/view</v>
+      </c>
+      <c r="H5" t="str">
+        <v>https://www.linkedin.com/in/priyapatel/</v>
+      </c>
+      <c r="I5" t="str">
+        <v>https://www.instagram.com/priya_designs/</v>
+      </c>
+      <c r="J5">
+        <v>9876500000</v>
+      </c>
+      <c r="K5" t="str">
+        <v>Passionate about creative design and branding for Alumni Cell events.</v>
+      </c>
+      <c r="L5" t="str">
+        <v>Design Core Member (2025-26)</v>
+      </c>
+      <c r="M5" t="str">
+        <v>Graphic Design, Sketching</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:P4"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:P5"/>
   </ignoredErrors>
 </worksheet>
 </file>